--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123711484</v>
+        <v>123711356</v>
       </c>
       <c r="B2" t="n">
-        <v>90931</v>
+        <v>57503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559920</v>
+        <v>559933</v>
       </c>
       <c r="R2" t="n">
-        <v>6583239</v>
+        <v>6583202</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123711356</v>
+        <v>123711878</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>57640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,7 +823,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -829,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559933</v>
+        <v>559904</v>
       </c>
       <c r="R3" t="n">
-        <v>6583202</v>
+        <v>6583225</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123711849</v>
+        <v>123711714</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559906</v>
+        <v>559917</v>
       </c>
       <c r="R4" t="n">
-        <v>6583241</v>
+        <v>6583225</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123711671</v>
+        <v>123711849</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559921</v>
+        <v>559906</v>
       </c>
       <c r="R5" t="n">
-        <v>6583235</v>
+        <v>6583241</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123711878</v>
+        <v>123711931</v>
       </c>
       <c r="B6" t="n">
-        <v>57634</v>
+        <v>98396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,35 +1121,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559904</v>
+        <v>559887</v>
       </c>
       <c r="R6" t="n">
-        <v>6583225</v>
+        <v>6583290</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,6 +1197,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1215,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123711437</v>
+        <v>123711671</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,16 +1249,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1267,13 +1260,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559920</v>
+        <v>559921</v>
       </c>
       <c r="R7" t="n">
-        <v>6583239</v>
+        <v>6583235</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123711462</v>
+        <v>123711626</v>
       </c>
       <c r="B8" t="n">
-        <v>105485</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,29 +1335,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1374,13 +1375,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559920</v>
+        <v>559917</v>
       </c>
       <c r="R8" t="n">
-        <v>6583239</v>
+        <v>6583248</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123711626</v>
+        <v>123711752</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>90983</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,39 +1450,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1489,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559917</v>
+        <v>559906</v>
       </c>
       <c r="R9" t="n">
-        <v>6583248</v>
+        <v>6583241</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123711714</v>
+        <v>123711462</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>105502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,25 +1556,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,13 +1588,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559917</v>
+        <v>559920</v>
       </c>
       <c r="R10" t="n">
-        <v>6583225</v>
+        <v>6583239</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123711931</v>
+        <v>123711437</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1692,8 +1684,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559887</v>
+        <v>559920</v>
       </c>
       <c r="R11" t="n">
-        <v>6583290</v>
+        <v>6583239</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123711752</v>
+        <v>123711484</v>
       </c>
       <c r="B12" t="n">
-        <v>90966</v>
+        <v>90948</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,25 +1778,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559906</v>
+        <v>559920</v>
       </c>
       <c r="R12" t="n">
-        <v>6583241</v>
+        <v>6583239</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123711356</v>
+        <v>123711878</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
+        <v>57643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559933</v>
+        <v>559904</v>
       </c>
       <c r="R2" t="n">
-        <v>6583202</v>
+        <v>6583225</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123711878</v>
+        <v>123711714</v>
       </c>
       <c r="B3" t="n">
-        <v>57640</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +797,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559904</v>
+        <v>559917</v>
       </c>
       <c r="R3" t="n">
         <v>6583225</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,6 +873,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123711714</v>
+        <v>123711931</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559917</v>
+        <v>559887</v>
       </c>
       <c r="R4" t="n">
-        <v>6583225</v>
+        <v>6583290</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123711849</v>
+        <v>123711752</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>90988</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,31 +1011,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1109,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123711931</v>
+        <v>123711626</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,8 +1138,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1153,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559887</v>
+        <v>559917</v>
       </c>
       <c r="R6" t="n">
-        <v>6583290</v>
+        <v>6583248</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1223,7 @@
         <v>123711671</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123711626</v>
+        <v>123711849</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,16 +1360,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1375,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559917</v>
+        <v>559906</v>
       </c>
       <c r="R8" t="n">
-        <v>6583248</v>
+        <v>6583241</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123711752</v>
+        <v>123711356</v>
       </c>
       <c r="B9" t="n">
-        <v>90983</v>
+        <v>57506</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,26 +1450,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1481,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559906</v>
+        <v>559933</v>
       </c>
       <c r="R9" t="n">
-        <v>6583241</v>
+        <v>6583202</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1526,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>123711462</v>
       </c>
       <c r="B10" t="n">
-        <v>105502</v>
+        <v>105518</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123711437</v>
+        <v>123711484</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>90953</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,39 +1663,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1766,10 +1757,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123711484</v>
+        <v>123711437</v>
       </c>
       <c r="B12" t="n">
-        <v>90948</v>
+        <v>98502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,30 +1769,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123711878</v>
+        <v>123711714</v>
       </c>
       <c r="B2" t="n">
-        <v>57643</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559904</v>
+        <v>559917</v>
       </c>
       <c r="R2" t="n">
         <v>6583225</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123711714</v>
+        <v>123711626</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,8 +815,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -832,7 +837,7 @@
         <v>559917</v>
       </c>
       <c r="R3" t="n">
-        <v>6583225</v>
+        <v>6583248</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123711931</v>
+        <v>123711752</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,31 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559887</v>
+        <v>559906</v>
       </c>
       <c r="R4" t="n">
-        <v>6583290</v>
+        <v>6583241</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123711752</v>
+        <v>123711849</v>
       </c>
       <c r="B5" t="n">
-        <v>90988</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,30 +1015,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1105,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123711626</v>
+        <v>123711671</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,16 +1143,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1157,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559917</v>
+        <v>559921</v>
       </c>
       <c r="R6" t="n">
-        <v>6583248</v>
+        <v>6583235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123711671</v>
+        <v>123711356</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,31 +1229,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1264,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559921</v>
+        <v>559933</v>
       </c>
       <c r="R7" t="n">
-        <v>6583235</v>
+        <v>6583202</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1309,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123711849</v>
+        <v>123711931</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559906</v>
+        <v>559887</v>
       </c>
       <c r="R8" t="n">
-        <v>6583241</v>
+        <v>6583290</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123711356</v>
+        <v>123711878</v>
       </c>
       <c r="B9" t="n">
-        <v>57506</v>
+        <v>57644</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1472,7 +1472,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1482,13 +1482,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559933</v>
+        <v>559904</v>
       </c>
       <c r="R9" t="n">
-        <v>6583202</v>
+        <v>6583225</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123711462</v>
+        <v>123711484</v>
       </c>
       <c r="B10" t="n">
-        <v>105518</v>
+        <v>90955</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,27 +1560,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1651,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123711484</v>
+        <v>123711437</v>
       </c>
       <c r="B11" t="n">
-        <v>90953</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,30 +1662,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1757,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123711437</v>
+        <v>123711462</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>105520</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,37 +1777,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123711626</v>
+        <v>123711752</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,39 +794,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559917</v>
+        <v>559906</v>
       </c>
       <c r="R3" t="n">
-        <v>6583248</v>
+        <v>6583241</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123711752</v>
+        <v>123711626</v>
       </c>
       <c r="B4" t="n">
-        <v>90990</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +900,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559906</v>
+        <v>559917</v>
       </c>
       <c r="R4" t="n">
-        <v>6583241</v>
+        <v>6583248</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123711714</v>
+        <v>123711752</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559917</v>
+        <v>559906</v>
       </c>
       <c r="R2" t="n">
-        <v>6583225</v>
+        <v>6583241</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123711752</v>
+        <v>123711714</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,30 +793,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559906</v>
+        <v>559917</v>
       </c>
       <c r="R3" t="n">
-        <v>6583241</v>
+        <v>6583225</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,7 +891,7 @@
         <v>123711626</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123711849</v>
+        <v>123711878</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,31 +1015,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1047,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559906</v>
+        <v>559904</v>
       </c>
       <c r="R5" t="n">
-        <v>6583241</v>
+        <v>6583225</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1095,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1110,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123711671</v>
+        <v>123711356</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,31 +1125,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559921</v>
+        <v>559933</v>
       </c>
       <c r="R6" t="n">
-        <v>6583235</v>
+        <v>6583202</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1205,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1217,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123711356</v>
+        <v>123711931</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,35 +1235,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1265,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559933</v>
+        <v>559887</v>
       </c>
       <c r="R7" t="n">
-        <v>6583202</v>
+        <v>6583290</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,6 +1311,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1327,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123711931</v>
+        <v>123711671</v>
       </c>
       <c r="B8" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559887</v>
+        <v>559921</v>
       </c>
       <c r="R8" t="n">
-        <v>6583290</v>
+        <v>6583235</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123711878</v>
+        <v>123711849</v>
       </c>
       <c r="B9" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,35 +1449,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1482,13 +1481,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559904</v>
+        <v>559906</v>
       </c>
       <c r="R9" t="n">
-        <v>6583225</v>
+        <v>6583241</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,6 +1525,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123711484</v>
+        <v>123711437</v>
       </c>
       <c r="B10" t="n">
-        <v>90955</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,30 +1556,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1650,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123711437</v>
+        <v>123711484</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>90955</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,39 +1671,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>123711462</v>
       </c>
       <c r="B12" t="n">
-        <v>105520</v>
+        <v>105095</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123711714</v>
+        <v>123711671</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559917</v>
+        <v>559921</v>
       </c>
       <c r="R3" t="n">
-        <v>6583225</v>
+        <v>6583235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123711878</v>
+        <v>123711849</v>
       </c>
       <c r="B5" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,35 +1015,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,13 +1047,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559904</v>
+        <v>559906</v>
       </c>
       <c r="R5" t="n">
-        <v>6583225</v>
+        <v>6583241</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,6 +1091,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1113,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123711356</v>
+        <v>123711878</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>57644</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,7 +1148,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1161,13 +1158,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559933</v>
+        <v>559904</v>
       </c>
       <c r="R6" t="n">
-        <v>6583202</v>
+        <v>6583225</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123711931</v>
+        <v>123711356</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,31 +1232,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1267,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559887</v>
+        <v>559933</v>
       </c>
       <c r="R7" t="n">
-        <v>6583290</v>
+        <v>6583202</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1312,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123711671</v>
+        <v>123711714</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559921</v>
+        <v>559917</v>
       </c>
       <c r="R8" t="n">
-        <v>6583235</v>
+        <v>6583225</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123711849</v>
+        <v>123711931</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559906</v>
+        <v>559887</v>
       </c>
       <c r="R9" t="n">
-        <v>6583241</v>
+        <v>6583290</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123711484</v>
+        <v>123711462</v>
       </c>
       <c r="B11" t="n">
-        <v>90955</v>
+        <v>105095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,26 +1675,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1765,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123711462</v>
+        <v>123711484</v>
       </c>
       <c r="B12" t="n">
-        <v>105095</v>
+        <v>90955</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,27 +1782,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123711752</v>
+        <v>123711931</v>
       </c>
       <c r="B2" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559906</v>
+        <v>559887</v>
       </c>
       <c r="R2" t="n">
-        <v>6583241</v>
+        <v>6583290</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123711671</v>
+        <v>123711878</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,31 +794,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559921</v>
+        <v>559904</v>
       </c>
       <c r="R3" t="n">
-        <v>6583235</v>
+        <v>6583225</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,7 +874,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -888,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123711626</v>
+        <v>123711671</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -921,16 +925,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -940,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559917</v>
+        <v>559921</v>
       </c>
       <c r="R4" t="n">
-        <v>6583248</v>
+        <v>6583235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123711849</v>
+        <v>123711626</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1036,8 +1032,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1047,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559906</v>
+        <v>559917</v>
       </c>
       <c r="R5" t="n">
-        <v>6583241</v>
+        <v>6583248</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123711878</v>
+        <v>123711752</v>
       </c>
       <c r="B6" t="n">
-        <v>57644</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,31 +1130,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1158,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559904</v>
+        <v>559906</v>
       </c>
       <c r="R6" t="n">
-        <v>6583225</v>
+        <v>6583241</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,6 +1201,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123711714</v>
+        <v>123711849</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559917</v>
+        <v>559906</v>
       </c>
       <c r="R8" t="n">
-        <v>6583225</v>
+        <v>6583241</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123711931</v>
+        <v>123711714</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559887</v>
+        <v>559917</v>
       </c>
       <c r="R9" t="n">
-        <v>6583290</v>
+        <v>6583225</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123711437</v>
+        <v>123711462</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,37 +1556,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1659,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123711462</v>
+        <v>123711484</v>
       </c>
       <c r="B11" t="n">
-        <v>105095</v>
+        <v>90955</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,27 +1667,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1766,10 +1757,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123711484</v>
+        <v>123711437</v>
       </c>
       <c r="B12" t="n">
-        <v>90955</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,30 +1769,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123711931</v>
+        <v>123711849</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559887</v>
+        <v>559906</v>
       </c>
       <c r="R2" t="n">
-        <v>6583290</v>
+        <v>6583241</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123711878</v>
+        <v>123711356</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,7 +820,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559904</v>
+        <v>559933</v>
       </c>
       <c r="R3" t="n">
-        <v>6583225</v>
+        <v>6583202</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123711671</v>
+        <v>123711878</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,31 +904,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,13 +940,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559921</v>
+        <v>559904</v>
       </c>
       <c r="R4" t="n">
-        <v>6583235</v>
+        <v>6583225</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,7 +984,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -999,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123711626</v>
+        <v>123711752</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,39 +1014,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559917</v>
+        <v>559906</v>
       </c>
       <c r="R5" t="n">
-        <v>6583248</v>
+        <v>6583241</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123711752</v>
+        <v>123711714</v>
       </c>
       <c r="B6" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,30 +1120,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1157,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559906</v>
+        <v>559917</v>
       </c>
       <c r="R6" t="n">
-        <v>6583241</v>
+        <v>6583225</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123711356</v>
+        <v>123711671</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,35 +1227,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1268,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559933</v>
+        <v>559921</v>
       </c>
       <c r="R7" t="n">
-        <v>6583202</v>
+        <v>6583235</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,6 +1303,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1330,7 +1322,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123711849</v>
+        <v>123711626</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1363,8 +1355,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559906</v>
+        <v>559917</v>
       </c>
       <c r="R8" t="n">
-        <v>6583241</v>
+        <v>6583248</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123711714</v>
+        <v>123711931</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559917</v>
+        <v>559887</v>
       </c>
       <c r="R9" t="n">
-        <v>6583225</v>
+        <v>6583290</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123711462</v>
+        <v>123711437</v>
       </c>
       <c r="B10" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,29 +1556,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1651,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123711484</v>
+        <v>123711462</v>
       </c>
       <c r="B11" t="n">
-        <v>90955</v>
+        <v>105095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1667,26 +1675,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1757,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123711437</v>
+        <v>123711484</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>90955</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,39 +1778,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1870,6 +1870,316 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128343982</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Oxmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>559875</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6583314</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128344325</v>
+      </c>
+      <c r="B14" t="n">
+        <v>105511</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Oxmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>559922</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6583251</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128343907</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91984</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Oxmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>559877</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6583306</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128343982</v>
+        <v>128344325</v>
       </c>
       <c r="B13" t="n">
-        <v>5177</v>
+        <v>105511</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,32 +1883,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1916,13 +1911,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559875</v>
+        <v>559922</v>
       </c>
       <c r="R13" t="n">
-        <v>6583314</v>
+        <v>6583251</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1979,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128344325</v>
+        <v>128343907</v>
       </c>
       <c r="B14" t="n">
-        <v>105511</v>
+        <v>91984</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,27 +1985,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2018,13 +2012,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559922</v>
+        <v>559877</v>
       </c>
       <c r="R14" t="n">
-        <v>6583251</v>
+        <v>6583306</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2078,107 +2072,6 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>128343907</v>
-      </c>
-      <c r="B15" t="n">
-        <v>91984</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1339</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Brandticka</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Pycnoporellus fulgens</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Oxmossen, Srm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>559877</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6583306</v>
-      </c>
-      <c r="S15" t="n">
-        <v>8</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Kung Karl</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -1875,7 +1875,7 @@
         <v>128344325</v>
       </c>
       <c r="B13" t="n">
-        <v>105511</v>
+        <v>105516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128343907</v>
       </c>
       <c r="B14" t="n">
-        <v>91984</v>
+        <v>91989</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -1875,7 +1875,7 @@
         <v>128344325</v>
       </c>
       <c r="B13" t="n">
-        <v>105516</v>
+        <v>105609</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128343907</v>
       </c>
       <c r="B14" t="n">
-        <v>91989</v>
+        <v>92081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -1875,7 +1875,7 @@
         <v>128344325</v>
       </c>
       <c r="B13" t="n">
-        <v>105609</v>
+        <v>105630</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128343907</v>
       </c>
       <c r="B14" t="n">
-        <v>92081</v>
+        <v>92093</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -1875,7 +1875,7 @@
         <v>128344325</v>
       </c>
       <c r="B13" t="n">
-        <v>105630</v>
+        <v>105642</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128343907</v>
       </c>
       <c r="B14" t="n">
-        <v>92093</v>
+        <v>92095</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -1875,7 +1875,7 @@
         <v>128344325</v>
       </c>
       <c r="B13" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -1875,7 +1875,7 @@
         <v>128344325</v>
       </c>
       <c r="B13" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128343907</v>
       </c>
       <c r="B14" t="n">
-        <v>92095</v>
+        <v>92096</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -1875,7 +1875,7 @@
         <v>128344325</v>
       </c>
       <c r="B13" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128343907</v>
       </c>
       <c r="B14" t="n">
-        <v>92096</v>
+        <v>92123</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -1875,7 +1875,7 @@
         <v>128344325</v>
       </c>
       <c r="B13" t="n">
-        <v>105682</v>
+        <v>105695</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128343907</v>
       </c>
       <c r="B14" t="n">
-        <v>92123</v>
+        <v>92133</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -1875,7 +1875,7 @@
         <v>128344325</v>
       </c>
       <c r="B13" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128343907</v>
       </c>
       <c r="B14" t="n">
-        <v>92133</v>
+        <v>92137</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -1977,7 +1977,7 @@
         <v>128343907</v>
       </c>
       <c r="B14" t="n">
-        <v>92137</v>
+        <v>92199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -1977,7 +1977,7 @@
         <v>128343907</v>
       </c>
       <c r="B14" t="n">
-        <v>92199</v>
+        <v>92200</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -1977,7 +1977,7 @@
         <v>128343907</v>
       </c>
       <c r="B14" t="n">
-        <v>92200</v>
+        <v>92203</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -1977,7 +1977,7 @@
         <v>128343907</v>
       </c>
       <c r="B14" t="n">
-        <v>92203</v>
+        <v>92231</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -1977,7 +1977,7 @@
         <v>128343907</v>
       </c>
       <c r="B14" t="n">
-        <v>92231</v>
+        <v>92237</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -1977,7 +1977,7 @@
         <v>128343907</v>
       </c>
       <c r="B14" t="n">
-        <v>92237</v>
+        <v>92238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -1977,7 +1977,7 @@
         <v>128343907</v>
       </c>
       <c r="B14" t="n">
-        <v>92238</v>
+        <v>92243</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -1977,7 +1977,7 @@
         <v>128343907</v>
       </c>
       <c r="B14" t="n">
-        <v>92243</v>
+        <v>92247</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -1977,7 +1977,7 @@
         <v>128343907</v>
       </c>
       <c r="B14" t="n">
-        <v>92247</v>
+        <v>92249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123711356</v>
+        <v>123711752</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559933</v>
+        <v>559906</v>
       </c>
       <c r="R2" t="n">
-        <v>6583202</v>
+        <v>6583241</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,43 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123711931</v>
+        <v>128343907</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +814,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559887</v>
+        <v>559877</v>
       </c>
       <c r="R3" t="n">
-        <v>6583290</v>
+        <v>6583306</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,12 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123711752</v>
+        <v>123711484</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -935,13 +915,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559906</v>
+        <v>559920</v>
       </c>
       <c r="R4" t="n">
-        <v>6583241</v>
+        <v>6583239</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,43 +978,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123711849</v>
+        <v>123711264</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1042,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559906</v>
+        <v>559937</v>
       </c>
       <c r="R5" t="n">
-        <v>6583241</v>
+        <v>6583210</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1065,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1105,43 +1083,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123711714</v>
+        <v>123711356</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1149,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559917</v>
+        <v>559933</v>
       </c>
       <c r="R6" t="n">
-        <v>6583225</v>
+        <v>6583202</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1170,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1212,43 +1188,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123711671</v>
+        <v>123711878</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1256,13 +1231,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559921</v>
+        <v>559904</v>
       </c>
       <c r="R7" t="n">
-        <v>6583235</v>
+        <v>6583225</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1275,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1319,15 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123711626</v>
+        <v>123711437</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,7 +1323,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1371,13 +1340,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559917</v>
+        <v>559920</v>
       </c>
       <c r="R8" t="n">
-        <v>6583248</v>
+        <v>6583239</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,47 +1403,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123711878</v>
+        <v>123711626</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1482,13 +1450,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559904</v>
+        <v>559917</v>
       </c>
       <c r="R9" t="n">
-        <v>6583225</v>
+        <v>6583248</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,6 +1494,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1544,37 +1513,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123711462</v>
+        <v>123711671</v>
       </c>
       <c r="B10" t="n">
-        <v>105117</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,13 +1552,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559920</v>
+        <v>559921</v>
       </c>
       <c r="R10" t="n">
-        <v>6583239</v>
+        <v>6583235</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,42 +1615,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123711484</v>
+        <v>123711714</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1694,13 +1654,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559920</v>
+        <v>559917</v>
       </c>
       <c r="R11" t="n">
-        <v>6583239</v>
+        <v>6583225</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1757,15 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123711437</v>
+        <v>123711849</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,16 +1745,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1809,13 +1756,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559920</v>
+        <v>559906</v>
       </c>
       <c r="R12" t="n">
-        <v>6583239</v>
+        <v>6583241</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1872,32 +1819,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128344325</v>
+        <v>123711931</v>
       </c>
       <c r="B13" t="n">
-        <v>105699</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,10 +1858,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559922</v>
+        <v>559887</v>
       </c>
       <c r="R13" t="n">
-        <v>6583251</v>
+        <v>6583290</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,12 +1888,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1921,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128343907</v>
+        <v>123711462</v>
       </c>
       <c r="B14" t="n">
-        <v>92249</v>
+        <v>106244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,26 +1932,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2012,13 +1960,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559877</v>
+        <v>559920</v>
       </c>
       <c r="R14" t="n">
-        <v>6583306</v>
+        <v>6583239</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2042,12 +1990,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2072,6 +2020,210 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128344325</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Oxmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>559922</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6583251</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123711295</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Oxmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>559953</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6583196</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8475-2025 artfynd.xlsx
+++ b/artfynd/A 8475-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123711752</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128343907</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123711484</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123711264</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123711356</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123711878</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123711437</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1510,6 +1550,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123711626</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1612,6 +1657,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123711671</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1714,6 +1764,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123711714</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1816,6 +1871,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123711849</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1918,6 +1978,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123711931</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2020,6 +2085,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123711462</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2122,6 +2192,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344325</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2224,8 +2299,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123711295</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>